--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O564"/>
+  <dimension ref="A1:O570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29210,6 +29210,312 @@
         <v>390.24</v>
       </c>
       <c r="O564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="C565" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="D565" t="n">
+        <v>349</v>
+      </c>
+      <c r="E565" t="n">
+        <v>359.39</v>
+      </c>
+      <c r="F565" t="n">
+        <v>363.89</v>
+      </c>
+      <c r="G565" t="n">
+        <v>372.61</v>
+      </c>
+      <c r="H565" t="n">
+        <v>367.43</v>
+      </c>
+      <c r="I565" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="J565" t="n">
+        <v>376.77</v>
+      </c>
+      <c r="K565" t="n">
+        <v>382.99</v>
+      </c>
+      <c r="L565" t="n">
+        <v>384.51</v>
+      </c>
+      <c r="M565" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="N565" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="C566" t="n">
+        <v>345.69</v>
+      </c>
+      <c r="D566" t="n">
+        <v>348.18</v>
+      </c>
+      <c r="E566" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="F566" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="G566" t="n">
+        <v>371.71</v>
+      </c>
+      <c r="H566" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="I566" t="n">
+        <v>369.16</v>
+      </c>
+      <c r="J566" t="n">
+        <v>376.43</v>
+      </c>
+      <c r="K566" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="L566" t="n">
+        <v>384.26</v>
+      </c>
+      <c r="M566" t="n">
+        <v>386.18</v>
+      </c>
+      <c r="N566" t="n">
+        <v>390.99</v>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>354.72</v>
+      </c>
+      <c r="C567" t="n">
+        <v>345.2</v>
+      </c>
+      <c r="D567" t="n">
+        <v>346.43</v>
+      </c>
+      <c r="E567" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="F567" t="n">
+        <v>362.36</v>
+      </c>
+      <c r="G567" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="H567" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="I567" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="J567" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="K567" t="n">
+        <v>382.46</v>
+      </c>
+      <c r="L567" t="n">
+        <v>383.36</v>
+      </c>
+      <c r="M567" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="N567" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="C568" t="n">
+        <v>343.99</v>
+      </c>
+      <c r="D568" t="n">
+        <v>345.63</v>
+      </c>
+      <c r="E568" t="n">
+        <v>357.17</v>
+      </c>
+      <c r="F568" t="n">
+        <v>362.08</v>
+      </c>
+      <c r="G568" t="n">
+        <v>370.93</v>
+      </c>
+      <c r="H568" t="n">
+        <v>365.75</v>
+      </c>
+      <c r="I568" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="J568" t="n">
+        <v>375.69</v>
+      </c>
+      <c r="K568" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="L568" t="n">
+        <v>383.27</v>
+      </c>
+      <c r="M568" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="N568" t="n">
+        <v>390.97</v>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>355.33</v>
+      </c>
+      <c r="C569" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="D569" t="n">
+        <v>346.38</v>
+      </c>
+      <c r="E569" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="F569" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="G569" t="n">
+        <v>371.31</v>
+      </c>
+      <c r="H569" t="n">
+        <v>366.83</v>
+      </c>
+      <c r="I569" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="J569" t="n">
+        <v>376.67</v>
+      </c>
+      <c r="K569" t="n">
+        <v>382.98</v>
+      </c>
+      <c r="L569" t="n">
+        <v>383.69</v>
+      </c>
+      <c r="M569" t="n">
+        <v>386.5</v>
+      </c>
+      <c r="N569" t="n">
+        <v>391.41</v>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="C570" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="D570" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="E570" t="n">
+        <v>358.13</v>
+      </c>
+      <c r="F570" t="n">
+        <v>362.92</v>
+      </c>
+      <c r="G570" t="n">
+        <v>371.87</v>
+      </c>
+      <c r="H570" t="n">
+        <v>367.36</v>
+      </c>
+      <c r="I570" t="n">
+        <v>370.64</v>
+      </c>
+      <c r="J570" t="n">
+        <v>378.41</v>
+      </c>
+      <c r="K570" t="n">
+        <v>384.12</v>
+      </c>
+      <c r="L570" t="n">
+        <v>384.09</v>
+      </c>
+      <c r="M570" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="N570" t="n">
+        <v>391.88</v>
+      </c>
+      <c r="O570" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29226,7 +29532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B581"/>
+  <dimension ref="A1:B587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35039,6 +35345,66 @@
       </c>
       <c r="B581" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -35207,28 +35573,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2458990735483552</v>
+        <v>-0.2627410395279056</v>
       </c>
       <c r="J2" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K2" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06203308707736555</v>
+        <v>0.07076245077484655</v>
       </c>
       <c r="M2" t="n">
-        <v>5.358047364833475</v>
+        <v>5.356289116288693</v>
       </c>
       <c r="N2" t="n">
-        <v>53.42060712211582</v>
+        <v>53.60527930037146</v>
       </c>
       <c r="O2" t="n">
-        <v>7.308940218808457</v>
+        <v>7.321562626951398</v>
       </c>
       <c r="P2" t="n">
-        <v>370.8741642629208</v>
+        <v>371.0504652272803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35285,28 +35651,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04602243421231782</v>
+        <v>0.02724145704564374</v>
       </c>
       <c r="J3" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K3" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003756939215153965</v>
+        <v>0.001312440650974578</v>
       </c>
       <c r="M3" t="n">
-        <v>4.700514674840425</v>
+        <v>4.72069198166566</v>
       </c>
       <c r="N3" t="n">
-        <v>32.81717720175883</v>
+        <v>33.3916963308031</v>
       </c>
       <c r="O3" t="n">
-        <v>5.728627863787176</v>
+        <v>5.778554865258537</v>
       </c>
       <c r="P3" t="n">
-        <v>353.4818237571648</v>
+        <v>353.6784150622519</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35363,28 +35729,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2121730726676515</v>
+        <v>0.1920328579792915</v>
       </c>
       <c r="J4" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K4" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08851985207573387</v>
+        <v>0.07258099673332752</v>
       </c>
       <c r="M4" t="n">
-        <v>4.07232116706148</v>
+        <v>4.093896042692104</v>
       </c>
       <c r="N4" t="n">
-        <v>27.08432249673299</v>
+        <v>27.86326491165809</v>
       </c>
       <c r="O4" t="n">
-        <v>5.204260033543001</v>
+        <v>5.278566558418875</v>
       </c>
       <c r="P4" t="n">
-        <v>351.5547753359085</v>
+        <v>351.7655995412257</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35441,28 +35807,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.261027926612637</v>
+        <v>0.2494677464538466</v>
       </c>
       <c r="J5" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K5" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1400141290218831</v>
+        <v>0.130377597480158</v>
       </c>
       <c r="M5" t="n">
-        <v>3.623311282207553</v>
+        <v>3.632176820691498</v>
       </c>
       <c r="N5" t="n">
-        <v>24.45255871865667</v>
+        <v>24.54620763725055</v>
       </c>
       <c r="O5" t="n">
-        <v>4.944952853026677</v>
+        <v>4.954412945773752</v>
       </c>
       <c r="P5" t="n">
-        <v>356.8497608147552</v>
+        <v>356.9707716299812</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35519,28 +35885,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2183937246198659</v>
+        <v>0.2087423803919471</v>
       </c>
       <c r="J6" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K6" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07549706124589783</v>
+        <v>0.07042263378727298</v>
       </c>
       <c r="M6" t="n">
-        <v>4.195612345714809</v>
+        <v>4.193392300026026</v>
       </c>
       <c r="N6" t="n">
-        <v>34.12632083027331</v>
+        <v>34.01123413001537</v>
       </c>
       <c r="O6" t="n">
-        <v>5.841773774314897</v>
+        <v>5.831915133986037</v>
       </c>
       <c r="P6" t="n">
-        <v>361.8463949282263</v>
+        <v>361.9474225460509</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35597,28 +35963,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1837936390344363</v>
+        <v>0.1787890318799529</v>
       </c>
       <c r="J7" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K7" t="n">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07535750668585328</v>
+        <v>0.0729195095470202</v>
       </c>
       <c r="M7" t="n">
-        <v>3.748880275486931</v>
+        <v>3.7286897294819</v>
       </c>
       <c r="N7" t="n">
-        <v>24.25684698262784</v>
+        <v>24.06935472153327</v>
       </c>
       <c r="O7" t="n">
-        <v>4.925124057587569</v>
+        <v>4.906052865749947</v>
       </c>
       <c r="P7" t="n">
-        <v>369.1312616634045</v>
+        <v>369.1836200585893</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35675,28 +36041,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2129501780450501</v>
+        <v>0.2038629253257903</v>
       </c>
       <c r="J8" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K8" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09029270893970387</v>
+        <v>0.08448268968031303</v>
       </c>
       <c r="M8" t="n">
-        <v>3.721800344451304</v>
+        <v>3.722669059371689</v>
       </c>
       <c r="N8" t="n">
-        <v>26.69536835086384</v>
+        <v>26.63196321557746</v>
       </c>
       <c r="O8" t="n">
-        <v>5.166756076191699</v>
+        <v>5.160616553821593</v>
       </c>
       <c r="P8" t="n">
-        <v>365.5502442398357</v>
+        <v>365.6453622780301</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35753,28 +36119,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2157374954748122</v>
+        <v>0.2088846217079579</v>
       </c>
       <c r="J9" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K9" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1249077061679473</v>
+        <v>0.1196852392110666</v>
       </c>
       <c r="M9" t="n">
-        <v>3.286283785386879</v>
+        <v>3.286742360906922</v>
       </c>
       <c r="N9" t="n">
-        <v>19.05227325956756</v>
+        <v>18.97746409004773</v>
       </c>
       <c r="O9" t="n">
-        <v>4.364890979115923</v>
+        <v>4.356313130394524</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0589061952131</v>
+        <v>367.130631959419</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35831,28 +36197,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1885302000658763</v>
+        <v>0.1799363399019143</v>
       </c>
       <c r="J10" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K10" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1013590277182778</v>
+        <v>0.09415994586223486</v>
       </c>
       <c r="M10" t="n">
-        <v>3.346369262368482</v>
+        <v>3.359106730874706</v>
       </c>
       <c r="N10" t="n">
-        <v>18.41266054793419</v>
+        <v>18.41835905660953</v>
       </c>
       <c r="O10" t="n">
-        <v>4.290997616864194</v>
+        <v>4.291661572935304</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8873912880822</v>
+        <v>375.9773354765237</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35909,28 +36275,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1407467976995045</v>
+        <v>0.1329098867626516</v>
       </c>
       <c r="J11" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K11" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07080133026074786</v>
+        <v>0.06433202887396261</v>
       </c>
       <c r="M11" t="n">
-        <v>2.893128161133635</v>
+        <v>2.905656404454473</v>
       </c>
       <c r="N11" t="n">
-        <v>15.19060660443753</v>
+        <v>15.19276924710113</v>
       </c>
       <c r="O11" t="n">
-        <v>3.897512874184963</v>
+        <v>3.89779030312062</v>
       </c>
       <c r="P11" t="n">
-        <v>383.1526478704653</v>
+        <v>383.2346701887341</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35987,28 +36353,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1616103713333422</v>
+        <v>0.1570694625565707</v>
       </c>
       <c r="J12" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K12" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07820512111308797</v>
+        <v>0.07554042099161284</v>
       </c>
       <c r="M12" t="n">
-        <v>3.216629001975251</v>
+        <v>3.206448876383707</v>
       </c>
       <c r="N12" t="n">
-        <v>17.98740297972867</v>
+        <v>17.85335710771692</v>
       </c>
       <c r="O12" t="n">
-        <v>4.241155854213409</v>
+        <v>4.225323313986389</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8038621295377</v>
+        <v>381.8513957973809</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36065,28 +36431,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1725956192574113</v>
+        <v>0.1680551523818703</v>
       </c>
       <c r="J13" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K13" t="n">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07466271927313173</v>
+        <v>0.07238557209516705</v>
       </c>
       <c r="M13" t="n">
-        <v>3.456136218202928</v>
+        <v>3.439433114631306</v>
       </c>
       <c r="N13" t="n">
-        <v>21.60417848547664</v>
+        <v>21.43300895182436</v>
       </c>
       <c r="O13" t="n">
-        <v>4.648029527173493</v>
+        <v>4.629579781343482</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9868793702647</v>
+        <v>384.034382783125</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36143,28 +36509,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2778314665515385</v>
+        <v>0.2777269331131654</v>
       </c>
       <c r="J14" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="K14" t="n">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1706081243344456</v>
+        <v>0.1736985144943873</v>
       </c>
       <c r="M14" t="n">
-        <v>3.464814124318366</v>
+        <v>3.432503580055599</v>
       </c>
       <c r="N14" t="n">
-        <v>21.93060812348214</v>
+        <v>21.7014090413125</v>
       </c>
       <c r="O14" t="n">
-        <v>4.683012718697456</v>
+        <v>4.658477116109137</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6366461167191</v>
+        <v>383.637733492735</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36202,7 +36568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O564"/>
+  <dimension ref="A1:O570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79621,6 +79987,468 @@
         </is>
       </c>
     </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:16:59+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-35.028756446471746,173.91637388881196</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-35.02928636651098,173.91573766601672</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-35.029891964960264,173.91522189329123</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>-35.03055345753347,173.91480573073903</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-35.03122672477878,173.91443446816956</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-35.03191860615159,173.9141691026409</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-35.03262314525025,173.9139415199855</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-35.03334950407067,173.91378901897505</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-35.034079092918084,173.91364467564728</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-35.034797105799235,173.91349504808198</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-35.035516522430854,173.91338660922372</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-35.03623544452621,173.9133014320247</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-35.03695834540718,173.91333076991143</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-35.028748827142685,173.9163612433761</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-35.02928189079427,173.91573023790335</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-35.029887710124356,173.91521454219892</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>-35.03054842127025,173.91479534287936</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-35.03122366726777,173.91442652539664</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>-35.03191624146458,173.91415966497846</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>-35.03262206701111,173.9139347394051</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>-35.03334816951248,173.9137816311182</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>-35.034078368126224,173.9136410541259</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>-35.03479628429733,173.91348977017367</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>-35.03551623297046,173.91338389128697</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>-35.036234895444935,173.91329103897073</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>-35.03695835795286,173.91333329128614</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-35.02873950278707,173.91634576819547</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-35.029279279959304,173.91572590483761</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-35.02987862968029,173.91519885389476</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>-35.03054636098047,173.91479109330078</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-35.031220877288504,173.91441927761684</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-35.03191411324565,173.91415117108266</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>-35.03262074916275,173.91392645202927</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>-35.03334747322107,173.91377777658428</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>-35.03407702512928,173.9136343436599</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>-35.03479621723594,173.91348933932403</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>-35.03551519091251,173.91337410671483</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>-35.036234496637974,173.91328349033165</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>-35.03695832304299,173.91332627528698</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:17:03+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-35.02873918309486,173.91634523761792</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-35.029272832794746,173.91571520481926</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-35.02987447861943,173.9151916820997</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>-35.03054329343766,173.91478476615077</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>-35.031219807159346,173.91441649764664</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>-35.03191419206859,173.9141514856714</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>-35.03262026994504,173.91392343843813</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>-35.033347569928225,173.9137783119362</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>-35.034076790637705,173.91363317199128</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>-35.03479695491115,173.91349407867023</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>-35.035515086706674,173.91337312825763</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>-35.036234693151606,173.9132872099509</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>-35.03695835686194,173.91333307203618</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-35.02874275299126,173.9163511624009</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-35.02927608301833,173.9157205990432</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-35.02987837023899,173.91519840565752</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>-35.030544621180105,173.9147875047679</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-35.03122263535769,173.9144238447109</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>-35.03191519049235,173.91415547046196</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>-35.03262211835585,173.91393506228988</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>-35.03334818885391,173.9137817381886</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>-35.03407887974402,173.91364361049392</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>-35.0347970890339,173.91349494036953</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>-35.03551557300052,173.91337769439127</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>-35.03623508039873,173.9132945397889</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>-35.036958380862245,173.9133378955356</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>-35.02874387191396,173.91635301942253</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>-35.02928103827675,173.91572882302472</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>-35.02988200241689,173.91520468097875</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>-35.030547688722784,173.91479383191808</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-35.0312230175466,173.91442483755745</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>-35.031916661853444,173.91416134278506</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>-35.03262302544592,173.91394076658767</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>-35.03335103204253,173.9137974775361</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>-35.03408258897136,173.91366214416317</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>-35.03479900028236,173.91350721958514</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>-35.03551603613735,173.91338204309</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>-35.03623532893023,173.9132992440133</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>-35.03695840649872,173.91334304791</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O570"/>
+  <dimension ref="A1:O574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29518,6 +29518,210 @@
       <c r="O570" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="C571" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="D571" t="n">
+        <v>347.08</v>
+      </c>
+      <c r="E571" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="F571" t="n">
+        <v>363.12</v>
+      </c>
+      <c r="G571" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="H571" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="I571" t="n">
+        <v>370.79</v>
+      </c>
+      <c r="J571" t="n">
+        <v>378.46</v>
+      </c>
+      <c r="K571" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="L571" t="n">
+        <v>384.17</v>
+      </c>
+      <c r="M571" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="N571" t="n">
+        <v>391.8</v>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="C572" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="D572" t="n">
+        <v>347.88</v>
+      </c>
+      <c r="E572" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="F572" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="G572" t="n">
+        <v>371.97</v>
+      </c>
+      <c r="H572" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="I572" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="J572" t="n">
+        <v>378.64</v>
+      </c>
+      <c r="K572" t="n">
+        <v>385.14</v>
+      </c>
+      <c r="L572" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="M572" t="n">
+        <v>387.61</v>
+      </c>
+      <c r="N572" t="n">
+        <v>391.99</v>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="C573" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="D573" t="n">
+        <v>348.43</v>
+      </c>
+      <c r="E573" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="F573" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="G573" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="H573" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="I573" t="n">
+        <v>371.35</v>
+      </c>
+      <c r="J573" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="K573" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="L573" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="M573" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="N573" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>357.36</v>
+      </c>
+      <c r="C574" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="D574" t="n">
+        <v>349.07</v>
+      </c>
+      <c r="E574" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="F574" t="n">
+        <v>364.06</v>
+      </c>
+      <c r="G574" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="H574" t="n">
+        <v>368.94</v>
+      </c>
+      <c r="I574" t="n">
+        <v>371.64</v>
+      </c>
+      <c r="J574" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="K574" t="n">
+        <v>385.54</v>
+      </c>
+      <c r="L574" t="n">
+        <v>384.49</v>
+      </c>
+      <c r="M574" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="N574" t="n">
+        <v>392.03</v>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29532,7 +29736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B587"/>
+  <dimension ref="A1:B591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35405,6 +35609,46 @@
       </c>
       <c r="B587" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
@@ -35573,28 +35817,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2627410395279056</v>
+        <v>-0.2723379822436923</v>
       </c>
       <c r="J2" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K2" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07076245077484655</v>
+        <v>0.07616492967636668</v>
       </c>
       <c r="M2" t="n">
-        <v>5.356289116288693</v>
+        <v>5.35081160512613</v>
       </c>
       <c r="N2" t="n">
-        <v>53.60527930037146</v>
+        <v>53.60579735976863</v>
       </c>
       <c r="O2" t="n">
-        <v>7.321562626951398</v>
+        <v>7.321598005884278</v>
       </c>
       <c r="P2" t="n">
-        <v>371.0504652272803</v>
+        <v>371.1511851072122</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35651,28 +35895,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02724145704564374</v>
+        <v>0.01666216303684105</v>
       </c>
       <c r="J3" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K3" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001312440650974578</v>
+        <v>0.0004919346340925834</v>
       </c>
       <c r="M3" t="n">
-        <v>4.72069198166566</v>
+        <v>4.726769221830361</v>
       </c>
       <c r="N3" t="n">
-        <v>33.3916963308031</v>
+        <v>33.61225059206406</v>
       </c>
       <c r="O3" t="n">
-        <v>5.778554865258537</v>
+        <v>5.797607316131722</v>
       </c>
       <c r="P3" t="n">
-        <v>353.6784150622519</v>
+        <v>353.7894467494867</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35729,28 +35973,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1920328579792915</v>
+        <v>0.1805415383515707</v>
       </c>
       <c r="J4" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K4" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07258099673332752</v>
+        <v>0.06442592521902413</v>
       </c>
       <c r="M4" t="n">
-        <v>4.093896042692104</v>
+        <v>4.104962426604824</v>
       </c>
       <c r="N4" t="n">
-        <v>27.86326491165809</v>
+        <v>28.20510507883547</v>
       </c>
       <c r="O4" t="n">
-        <v>5.278566558418875</v>
+        <v>5.310847868169025</v>
       </c>
       <c r="P4" t="n">
-        <v>351.7655995412257</v>
+        <v>351.886201549447</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35807,28 +36051,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2494677464538466</v>
+        <v>0.2425064489295379</v>
       </c>
       <c r="J5" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K5" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L5" t="n">
-        <v>0.130377597480158</v>
+        <v>0.1248201191263025</v>
       </c>
       <c r="M5" t="n">
-        <v>3.632176820691498</v>
+        <v>3.636229580682321</v>
       </c>
       <c r="N5" t="n">
-        <v>24.54620763725055</v>
+        <v>24.57057087692775</v>
       </c>
       <c r="O5" t="n">
-        <v>4.954412945773752</v>
+        <v>4.95687107729541</v>
       </c>
       <c r="P5" t="n">
-        <v>356.9707716299812</v>
+        <v>357.0438342986928</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35885,28 +36129,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2087423803919471</v>
+        <v>0.2036131453164275</v>
       </c>
       <c r="J6" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K6" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07042263378727298</v>
+        <v>0.06795930830740693</v>
       </c>
       <c r="M6" t="n">
-        <v>4.193392300026026</v>
+        <v>4.186525449386205</v>
       </c>
       <c r="N6" t="n">
-        <v>34.01123413001537</v>
+        <v>33.88078616669349</v>
       </c>
       <c r="O6" t="n">
-        <v>5.831915133986037</v>
+        <v>5.820720416468522</v>
       </c>
       <c r="P6" t="n">
-        <v>361.9474225460509</v>
+        <v>362.0012540211413</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35963,28 +36207,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1787890318799529</v>
+        <v>0.1762671703776888</v>
       </c>
       <c r="J7" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K7" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0729195095470202</v>
+        <v>0.07192209734265731</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7286897294819</v>
+        <v>3.71240034424539</v>
       </c>
       <c r="N7" t="n">
-        <v>24.06935472153327</v>
+        <v>23.92725002338592</v>
       </c>
       <c r="O7" t="n">
-        <v>4.906052865749947</v>
+        <v>4.89154883685995</v>
       </c>
       <c r="P7" t="n">
-        <v>369.1836200585893</v>
+        <v>369.2100704396362</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36041,28 +36285,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2038629253257903</v>
+        <v>0.2000520447954193</v>
       </c>
       <c r="J8" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K8" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08448268968031303</v>
+        <v>0.08254355349250275</v>
       </c>
       <c r="M8" t="n">
-        <v>3.722669059371689</v>
+        <v>3.713705296225895</v>
       </c>
       <c r="N8" t="n">
-        <v>26.63196321557746</v>
+        <v>26.50600130364718</v>
       </c>
       <c r="O8" t="n">
-        <v>5.160616553821593</v>
+        <v>5.148397935634655</v>
       </c>
       <c r="P8" t="n">
-        <v>365.6453622780301</v>
+        <v>365.6853547732043</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36119,28 +36363,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2088846217079579</v>
+        <v>0.2069244004739212</v>
       </c>
       <c r="J9" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K9" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1196852392110666</v>
+        <v>0.119154767954054</v>
       </c>
       <c r="M9" t="n">
-        <v>3.286742360906922</v>
+        <v>3.274012394516228</v>
       </c>
       <c r="N9" t="n">
-        <v>18.97746409004773</v>
+        <v>18.86112198500431</v>
       </c>
       <c r="O9" t="n">
-        <v>4.356313130394524</v>
+        <v>4.342939325503444</v>
       </c>
       <c r="P9" t="n">
-        <v>367.130631959419</v>
+        <v>367.151202243695</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36197,28 +36441,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1799363399019143</v>
+        <v>0.1774044192154778</v>
       </c>
       <c r="J10" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K10" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09415994586223486</v>
+        <v>0.09287565975684753</v>
       </c>
       <c r="M10" t="n">
-        <v>3.359106730874706</v>
+        <v>3.349867999108203</v>
       </c>
       <c r="N10" t="n">
-        <v>18.41835905660953</v>
+        <v>18.31680435298988</v>
       </c>
       <c r="O10" t="n">
-        <v>4.291661572935304</v>
+        <v>4.279813588579517</v>
       </c>
       <c r="P10" t="n">
-        <v>375.9773354765237</v>
+        <v>376.0039045272719</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36275,28 +36519,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1329098867626516</v>
+        <v>0.1307657518598806</v>
       </c>
       <c r="J11" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K11" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06433202887396261</v>
+        <v>0.06319001405999347</v>
       </c>
       <c r="M11" t="n">
-        <v>2.905656404454473</v>
+        <v>2.897316269064834</v>
       </c>
       <c r="N11" t="n">
-        <v>15.19276924710113</v>
+        <v>15.1059144199986</v>
       </c>
       <c r="O11" t="n">
-        <v>3.89779030312062</v>
+        <v>3.886632786873311</v>
       </c>
       <c r="P11" t="n">
-        <v>383.2346701887341</v>
+        <v>383.2571708105303</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36353,28 +36597,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1570694625565707</v>
+        <v>0.1549436760878614</v>
       </c>
       <c r="J12" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K12" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07554042099161284</v>
+        <v>0.07459456525601649</v>
       </c>
       <c r="M12" t="n">
-        <v>3.206448876383707</v>
+        <v>3.195153245945323</v>
       </c>
       <c r="N12" t="n">
-        <v>17.85335710771692</v>
+        <v>17.74714508247177</v>
       </c>
       <c r="O12" t="n">
-        <v>4.225323313986389</v>
+        <v>4.212736056587426</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8513957973809</v>
+        <v>381.873706695045</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36431,28 +36675,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1680551523818703</v>
+        <v>0.1669168752160473</v>
       </c>
       <c r="J13" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K13" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07238557209516705</v>
+        <v>0.0724379557952104</v>
       </c>
       <c r="M13" t="n">
-        <v>3.439433114631306</v>
+        <v>3.420367044267424</v>
       </c>
       <c r="N13" t="n">
-        <v>21.43300895182436</v>
+        <v>21.28920976153486</v>
       </c>
       <c r="O13" t="n">
-        <v>4.629579781343482</v>
+        <v>4.614023164390797</v>
       </c>
       <c r="P13" t="n">
-        <v>384.034382783125</v>
+        <v>384.0463201470633</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36509,28 +36753,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2777269331131654</v>
+        <v>0.2787933529263458</v>
       </c>
       <c r="J14" t="n">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="K14" t="n">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1736985144943873</v>
+        <v>0.1768944996359955</v>
       </c>
       <c r="M14" t="n">
-        <v>3.432503580055599</v>
+        <v>3.413939669489003</v>
       </c>
       <c r="N14" t="n">
-        <v>21.7014090413125</v>
+        <v>21.5542865538879</v>
       </c>
       <c r="O14" t="n">
-        <v>4.658477116109137</v>
+        <v>4.642659426868171</v>
       </c>
       <c r="P14" t="n">
-        <v>383.637733492735</v>
+        <v>383.626533408194</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36568,7 +36812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O570"/>
+  <dimension ref="A1:O574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80449,6 +80693,314 @@
         </is>
       </c>
     </row>
+    <row r="571">
+      <c r="A571" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>-35.02874387191396,173.91635301942253</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>-35.02928103827675,173.91572882302472</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>-35.02988200241689,173.91520468097875</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>-35.030548375486035,173.91479524844428</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-35.03122378192445,173.9144268232506</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>-35.03191632028751,173.9141599795672</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>-35.03262381273144,173.91394571748774</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>-35.03335132216371,173.91379908359204</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>-35.034082695558304,173.91366267673988</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>-35.03479997267144,173.91351346690558</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>-35.0355161287647,173.91338291282975</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>-35.0362354676454,173.91330186962696</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>-35.036958402135085,173.91334217091006</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-35.02874914683483,173.91636177395378</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-35.029283649111605,173.91573315609068</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-35.029886153476944,173.91521185277512</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-35.03054778029122,173.9147940207882</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-35.03122531068,173.914430794637</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-35.031916924596466,173.9141623914142</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-35.03262393253573,173.9139464708856</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>-35.03335221186849,173.91380400883025</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>-35.03408307927132,173.9136645940161</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>-35.034800710345706,173.91351820625218</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>-35.03551656874452,173.9133870440936</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>-35.03623572195641,173.913306683252</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>-35.03695841249872,173.91334425378483</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-35.028751278115806,173.91636531113843</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-35.02928647307564,173.91573784287658</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-35.02988900733047,173.91521678338555</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-35.030548375486035,173.91479524844428</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-35.03122657190325,173.9144340710309</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-35.03191721361379,173.91416354490627</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-35.03262448021246,173.91394991499004</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>-35.03335240528256,173.91380507953426</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>-35.03408361220599,173.91366725689977</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>-35.03480097859084,173.913519929651</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>-35.03551662663657,173.91338758768097</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>-35.03623588957038,173.91330985586848</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>-35.03695841086236,173.91334392490987</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-35.028753569242745,173.91636911361212</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-35.029289030627844,173.91574208751317</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-35.02989232817795,173.91522252082353</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-35.03055025263879,173.91479912028274</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-35.03122737449981,173.9144361560089</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-35.03191829086004,173.91416784428588</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-35.03262572959964,173.91395777185352</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>-35.03335296618327,173.91380818457583</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>-35.03408499783586,173.9136741803975</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>-35.0348013809585,173.9135225147492</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>-35.03551649927403,173.9133863917888</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>-35.03623599938639,173.91331193447928</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>-35.03695841468053,173.91334469228477</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O574"/>
+  <dimension ref="A1:O576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29722,6 +29722,108 @@
       <c r="O574" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>357.56</v>
+      </c>
+      <c r="C575" t="n">
+        <v>347.46</v>
+      </c>
+      <c r="D575" t="n">
+        <v>349.31</v>
+      </c>
+      <c r="E575" t="n">
+        <v>359.02</v>
+      </c>
+      <c r="F575" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="G575" t="n">
+        <v>372.79</v>
+      </c>
+      <c r="H575" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="I575" t="n">
+        <v>372.19</v>
+      </c>
+      <c r="J575" t="n">
+        <v>380.19</v>
+      </c>
+      <c r="K575" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="L575" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="M575" t="n">
+        <v>388.85</v>
+      </c>
+      <c r="N575" t="n">
+        <v>392.29</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>358.28</v>
+      </c>
+      <c r="C576" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="D576" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="E576" t="n">
+        <v>359.47</v>
+      </c>
+      <c r="F576" t="n">
+        <v>364.66</v>
+      </c>
+      <c r="G576" t="n">
+        <v>373.11</v>
+      </c>
+      <c r="H576" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="I576" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="J576" t="n">
+        <v>380.47</v>
+      </c>
+      <c r="K576" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="L576" t="n">
+        <v>386.31</v>
+      </c>
+      <c r="M576" t="n">
+        <v>389.67</v>
+      </c>
+      <c r="N576" t="n">
+        <v>393</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29736,7 +29838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B591"/>
+  <dimension ref="A1:B593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35649,6 +35751,26 @@
       </c>
       <c r="B591" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -35817,28 +35939,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2723379822436923</v>
+        <v>-0.2761419628555735</v>
       </c>
       <c r="J2" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K2" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07616492967636668</v>
+        <v>0.07850557937385239</v>
       </c>
       <c r="M2" t="n">
-        <v>5.35081160512613</v>
+        <v>5.344871625636666</v>
       </c>
       <c r="N2" t="n">
-        <v>53.60579735976863</v>
+        <v>53.53817415305754</v>
       </c>
       <c r="O2" t="n">
-        <v>7.321598005884278</v>
+        <v>7.316978485212154</v>
       </c>
       <c r="P2" t="n">
-        <v>371.1511851072122</v>
+        <v>371.1912608836166</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35895,28 +36017,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01666216303684105</v>
+        <v>0.01249221180960606</v>
       </c>
       <c r="J3" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K3" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004919346340925834</v>
+        <v>0.0002774178261687466</v>
       </c>
       <c r="M3" t="n">
-        <v>4.726769221830361</v>
+        <v>4.725591598109133</v>
       </c>
       <c r="N3" t="n">
-        <v>33.61225059206406</v>
+        <v>33.63801581342789</v>
       </c>
       <c r="O3" t="n">
-        <v>5.797607316131722</v>
+        <v>5.799828946911098</v>
       </c>
       <c r="P3" t="n">
-        <v>353.7894467494867</v>
+        <v>353.8333781268013</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35973,28 +36095,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1805415383515707</v>
+        <v>0.1759414079174046</v>
       </c>
       <c r="J4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K4" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06442592521902413</v>
+        <v>0.06144862560455577</v>
       </c>
       <c r="M4" t="n">
-        <v>4.104962426604824</v>
+        <v>4.107151537457215</v>
       </c>
       <c r="N4" t="n">
-        <v>28.20510507883547</v>
+        <v>28.28059590171267</v>
       </c>
       <c r="O4" t="n">
-        <v>5.310847868169025</v>
+        <v>5.317950347804374</v>
       </c>
       <c r="P4" t="n">
-        <v>351.886201549447</v>
+        <v>351.9346649679404</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36051,28 +36173,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2425064489295379</v>
+        <v>0.239681817119531</v>
       </c>
       <c r="J5" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K5" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1248201191263025</v>
+        <v>0.1227790852126939</v>
       </c>
       <c r="M5" t="n">
-        <v>3.636229580682321</v>
+        <v>3.635764516168709</v>
       </c>
       <c r="N5" t="n">
-        <v>24.57057087692775</v>
+        <v>24.55055506214461</v>
       </c>
       <c r="O5" t="n">
-        <v>4.95687107729541</v>
+        <v>4.954851669035573</v>
       </c>
       <c r="P5" t="n">
-        <v>357.0438342986928</v>
+        <v>357.0735924373906</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36129,28 +36251,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2036131453164275</v>
+        <v>0.2016268962910303</v>
       </c>
       <c r="J6" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K6" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06795930830740693</v>
+        <v>0.06712288381436804</v>
       </c>
       <c r="M6" t="n">
-        <v>4.186525449386205</v>
+        <v>4.180555665120492</v>
       </c>
       <c r="N6" t="n">
-        <v>33.88078616669349</v>
+        <v>33.79537865240427</v>
       </c>
       <c r="O6" t="n">
-        <v>5.820720416468522</v>
+        <v>5.813379279937295</v>
       </c>
       <c r="P6" t="n">
-        <v>362.0012540211413</v>
+        <v>362.0221795813823</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36207,28 +36329,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1762671703776888</v>
+        <v>0.1755998917295928</v>
       </c>
       <c r="J7" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K7" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07192209734265731</v>
+        <v>0.07189126719615369</v>
       </c>
       <c r="M7" t="n">
-        <v>3.71240034424539</v>
+        <v>3.702044764685683</v>
       </c>
       <c r="N7" t="n">
-        <v>23.92725002338592</v>
+        <v>23.84762124963147</v>
       </c>
       <c r="O7" t="n">
-        <v>4.89154883685995</v>
+        <v>4.883402630301076</v>
       </c>
       <c r="P7" t="n">
-        <v>369.2100704396362</v>
+        <v>369.2170964172835</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36285,28 +36407,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2000520447954193</v>
+        <v>0.1991078355466954</v>
       </c>
       <c r="J8" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K8" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08254355349250275</v>
+        <v>0.08235774165103205</v>
       </c>
       <c r="M8" t="n">
-        <v>3.713705296225895</v>
+        <v>3.705007489923527</v>
       </c>
       <c r="N8" t="n">
-        <v>26.50600130364718</v>
+        <v>26.42118137289814</v>
       </c>
       <c r="O8" t="n">
-        <v>5.148397935634655</v>
+        <v>5.140153827746611</v>
       </c>
       <c r="P8" t="n">
-        <v>365.6853547732043</v>
+        <v>365.6953021992603</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36363,28 +36485,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2069244004739212</v>
+        <v>0.206726428008851</v>
       </c>
       <c r="J9" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K9" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.119154767954054</v>
+        <v>0.1197165286815193</v>
       </c>
       <c r="M9" t="n">
-        <v>3.274012394516228</v>
+        <v>3.263644271293457</v>
       </c>
       <c r="N9" t="n">
-        <v>18.86112198500431</v>
+        <v>18.79606711496378</v>
       </c>
       <c r="O9" t="n">
-        <v>4.342939325503444</v>
+        <v>4.335443127866375</v>
       </c>
       <c r="P9" t="n">
-        <v>367.151202243695</v>
+        <v>367.1532878259935</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36441,28 +36563,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1774044192154778</v>
+        <v>0.1770966049630581</v>
       </c>
       <c r="J10" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K10" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09287565975684753</v>
+        <v>0.0931934004176469</v>
       </c>
       <c r="M10" t="n">
-        <v>3.349867999108203</v>
+        <v>3.339925875105704</v>
       </c>
       <c r="N10" t="n">
-        <v>18.31680435298988</v>
+        <v>18.25393664841097</v>
       </c>
       <c r="O10" t="n">
-        <v>4.279813588579517</v>
+        <v>4.272462597660859</v>
       </c>
       <c r="P10" t="n">
-        <v>376.0039045272719</v>
+        <v>376.0071473713265</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36519,28 +36641,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1307657518598806</v>
+        <v>0.130212821193593</v>
       </c>
       <c r="J11" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K11" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06319001405999347</v>
+        <v>0.06310979917944981</v>
       </c>
       <c r="M11" t="n">
-        <v>2.897316269064834</v>
+        <v>2.890341984271615</v>
       </c>
       <c r="N11" t="n">
-        <v>15.1059144199986</v>
+        <v>15.0558732254536</v>
       </c>
       <c r="O11" t="n">
-        <v>3.886632786873311</v>
+        <v>3.880189843996502</v>
       </c>
       <c r="P11" t="n">
-        <v>383.2571708105303</v>
+        <v>383.2629960797518</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36597,28 +36719,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1549436760878614</v>
+        <v>0.1547357533542414</v>
       </c>
       <c r="J12" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K12" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07459456525601649</v>
+        <v>0.07490692649526987</v>
       </c>
       <c r="M12" t="n">
-        <v>3.195153245945323</v>
+        <v>3.185978071837404</v>
       </c>
       <c r="N12" t="n">
-        <v>17.74714508247177</v>
+        <v>17.68688502706873</v>
       </c>
       <c r="O12" t="n">
-        <v>4.212736056587426</v>
+        <v>4.205577846987109</v>
       </c>
       <c r="P12" t="n">
-        <v>381.873706695045</v>
+        <v>381.8758969736576</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36675,28 +36797,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1669168752160473</v>
+        <v>0.1673706345267333</v>
       </c>
       <c r="J13" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K13" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0724379557952104</v>
+        <v>0.07328926029666127</v>
       </c>
       <c r="M13" t="n">
-        <v>3.420367044267424</v>
+        <v>3.411312685289524</v>
       </c>
       <c r="N13" t="n">
-        <v>21.28920976153486</v>
+        <v>21.21731384075647</v>
       </c>
       <c r="O13" t="n">
-        <v>4.614023164390797</v>
+        <v>4.606225552527413</v>
       </c>
       <c r="P13" t="n">
-        <v>384.0463201470633</v>
+        <v>384.041541646512</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36753,28 +36875,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2787933529263458</v>
+        <v>0.2797485421903741</v>
       </c>
       <c r="J14" t="n">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K14" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1768944996359955</v>
+        <v>0.1789057762512483</v>
       </c>
       <c r="M14" t="n">
-        <v>3.413939669489003</v>
+        <v>3.406862147469864</v>
       </c>
       <c r="N14" t="n">
-        <v>21.5542865538879</v>
+        <v>21.48709303702517</v>
       </c>
       <c r="O14" t="n">
-        <v>4.642659426868171</v>
+        <v>4.635417245192192</v>
       </c>
       <c r="P14" t="n">
-        <v>383.626533408194</v>
+        <v>383.6164645096384</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36812,7 +36934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O574"/>
+  <dimension ref="A1:O576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81001,6 +81123,160 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:17:25+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-35.02875463488313,173.91637088220463</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-35.02929132176821,173.9157458900003</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-35.029893573495684,173.91522467236288</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-35.030551763517764,173.91480223664064</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-35.0312280242208,173.91443784384825</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-35.031919079088915,173.91417099017346</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-35.03262667091842,173.91396369140833</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>-35.03335402996028,173.91381407344784</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>-35.03408638346533,173.91368110389544</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>-35.03480205157115,173.91352682324626</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>-35.035517298184416,173.9133938932943</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>-35.03623643865005,173.91332024892262</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>-35.036958428862285,173.91334754253444</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-35.028758471188326,173.91637724913798</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-35.02929505153133,173.91575208009613</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-35.029897413225115,173.91523130627635</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-35.03055382380712,173.91480648621982</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-35.03122966763263,173.91444211308908</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-35.03191991986628,173.91417434578693</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-35.0326271843649,173.91396692025648</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>-35.03335501637141,173.91381953403845</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>-35.03408698035176,173.9136840863254</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>-35.03480205157115,173.91352682324626</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>-35.035518606543924,173.91340617836886</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>-35.03623691259176,173.91332921976945</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>-35.036958467589024,173.9133553259085</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
